--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,6 +597,46 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>Baseline for reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-04-19 03:14:00</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Weighted BCE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet34 encoder)</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.1496</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9641999999999999</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9418</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.9527</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9101</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>BCE with positive weights to differentiate the small objects in the foreground to the background</t>
         </is>
       </c>
     </row>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -637,6 +637,46 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>BCE with positive weights to differentiate the small objects in the foreground to the background</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-04-19 03:16:24</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>adamax</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet34 encoder)</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>24</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9506</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9586</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9545</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Training with the adamax optimizer</t>
         </is>
       </c>
     </row>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -677,6 +677,46 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>Training with the adamax optimizer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-04-19 03:20:02</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Jaccard loss</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet34 encoder)</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>22</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.09180000000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.9505</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9592000000000001</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9547</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9137</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Training with the Jaccard loss</t>
         </is>
       </c>
     </row>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,6 +717,46 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>Training with the Jaccard loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-04-19 03:21:57</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tversky loss</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet34 encoder)</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>24</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0424</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.9253</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9777</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.9507</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.9064</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Training with the Tversky loss</t>
         </is>
       </c>
     </row>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,6 +757,46 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>Training with the Tversky loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-04-19 03:39:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ResNet50</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>34</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1484</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.9532</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9559</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.9544</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.9132</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Training with the ResNet50 encoder</t>
         </is>
       </c>
     </row>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,6 +800,46 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-19 03:40:57</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ResNet101</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet101 encoder)</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>14</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.9465</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9510999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.9025</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Training with the ResNet101 encoder</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -840,6 +840,46 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-19 03:56:30</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ssl weights</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.1683</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9421</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9484</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.9023</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Training with the ssl weights</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -880,6 +880,46 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-19 04:12:26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tversky loss parameter tuning</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9725</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9295</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9502</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9056999999999999</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Training with Tversky loss higher alpha (0.7) than betas (0.3) and 0.5e-4 lr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,6 +920,46 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-19 04:15:08</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tversky loss parameter tuning</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>23</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0515</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.9616</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9419999999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9514</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9078000000000001</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Training with Tversky loss higher alpha (0.7) than betas (0.3) and 0.5e-4 lr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,6 +960,46 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-19 04:21:36</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tversky loss parameter tuning</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>28</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1468</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9619</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9471000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9543</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Training with Tversky loss higher alpha (0.7) than betas (0.3) and 0.5e-4 lr</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1040,6 +1040,46 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-19 12:06:58</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Light data augmentation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>39</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.1519</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.9654</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9381</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.9513</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.9077</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Light data augmentation with a higher lr, and longer patience</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,6 +1080,46 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-19 12:10:26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Moderate data augmentation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1488</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.9552</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9530999999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.9539</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9123</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Moderate data augmentation with a higher lr, and longer patience</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1120,6 +1120,46 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-19 12:13:09</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Heavy data augmentation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>50</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.1767</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.9651999999999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.9429</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.893</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Heavy data augmentation with a higher lr, and longer patience</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,6 +1160,46 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-19 12:23:11</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tversky moderate data augmentation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>34</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0682</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.9556</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.9331</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8761</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Heavy data augmentation with a higher lr, and longer patience. Using Tversky loss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1200,6 +1200,46 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-20 03:54:17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tversky moderate data augmentation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>30</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.9464</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9554</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.9506</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9062</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Heavy data augmentation with a higher lr, and longer patience. Using Tversky loss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1240,6 +1240,46 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-20 04:02:34</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tversky moderate data augmentation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>U-Net (ResNet50 encoder)</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>35</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.9557</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9472</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.9512</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.9073</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Heavy data augmentation with a higher lr, and longer patience. Using Tversky loss</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/dl/gn/training_results_history.xlsx
+++ b/dl/gn/training_results_history.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3c90d80cead8d213/Desktop/Uni/Code/COMP9517/Assignment/COMP9517-Group-Project/dl/gn/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_6454BDDD01DD72B544D2E54BE9F18F49B758FEA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="6540" yWindow="1155" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -211,8 +217,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -270,44 +275,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -318,10 +320,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="1F497D"/>
@@ -359,71 +361,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -451,7 +453,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -474,11 +476,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -487,13 +489,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -503,7 +505,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -512,7 +514,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -521,7 +523,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -529,10 +531,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -597,26 +599,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="8" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="9" width="14.147857142857141" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="7" width="14.147857142857141" customWidth="1" bestFit="1"/>
+    <col min="1" max="3" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="14.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
+    <row r="1" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -648,611 +644,611 @@
         <v>9</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>39</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>0.1958</v>
       </c>
-      <c r="F2" s="6">
-        <v>0.9414</v>
-      </c>
-      <c r="G2" s="6">
-        <v>0.9467</v>
-      </c>
-      <c r="H2" s="6">
-        <v>0.9439</v>
-      </c>
-      <c r="I2" s="6">
-        <v>0.8938</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="F2" s="5">
+        <v>0.94140000000000001</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.94669999999999999</v>
+      </c>
+      <c r="H2" s="5">
+        <v>0.94389999999999996</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0.89380000000000004</v>
+      </c>
+      <c r="J2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>28</v>
       </c>
-      <c r="E3" s="6">
-        <v>0.1685</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0.9537</v>
-      </c>
-      <c r="G3" s="6">
-        <v>0.9467</v>
-      </c>
-      <c r="H3" s="6">
-        <v>0.9499</v>
-      </c>
-      <c r="I3" s="6">
-        <v>0.9051</v>
-      </c>
-      <c r="J3" s="4" t="s">
+      <c r="E3" s="5">
+        <v>0.16850000000000001</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.95369999999999999</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.94669999999999999</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.94989999999999997</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0.90510000000000002</v>
+      </c>
+      <c r="J3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>22</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>0.1663</v>
       </c>
-      <c r="F4" s="6">
-        <v>0.9413</v>
-      </c>
-      <c r="G4" s="6">
-        <v>0.959</v>
-      </c>
-      <c r="H4" s="6">
-        <v>0.9499</v>
-      </c>
-      <c r="I4" s="6">
-        <v>0.905</v>
-      </c>
-      <c r="J4" s="4" t="s">
+      <c r="F4" s="5">
+        <v>0.94130000000000003</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.94989999999999997</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="J4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>32</v>
       </c>
-      <c r="E5" s="6">
-        <v>0.1496</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.9642</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0.9418</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0.9527</v>
-      </c>
-      <c r="I5" s="6">
-        <v>0.9101</v>
-      </c>
-      <c r="J5" s="4" t="s">
+      <c r="E5" s="5">
+        <v>0.14960000000000001</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.96419999999999995</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.94179999999999997</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.95269999999999999</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0.91010000000000002</v>
+      </c>
+      <c r="J5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>24</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>0.151</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>0.9506</v>
       </c>
-      <c r="G6" s="6">
-        <v>0.9586</v>
-      </c>
-      <c r="H6" s="6">
-        <v>0.9545</v>
-      </c>
-      <c r="I6" s="6">
+      <c r="G6" s="5">
+        <v>0.95860000000000001</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.95450000000000002</v>
+      </c>
+      <c r="I6" s="5">
         <v>0.9133</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" t="s">
         <v>23</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>22</v>
       </c>
-      <c r="E7" s="6">
-        <v>0.0918</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0.9505</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0.9592</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0.9547</v>
-      </c>
-      <c r="I7" s="6">
-        <v>0.9137</v>
-      </c>
-      <c r="J7" s="4" t="s">
+      <c r="E7" s="5">
+        <v>9.1800000000000007E-2</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.95050000000000001</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.95920000000000005</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.95469999999999999</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.91369999999999996</v>
+      </c>
+      <c r="J7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>24</v>
       </c>
-      <c r="E8" s="6">
-        <v>0.0424</v>
-      </c>
-      <c r="F8" s="6">
-        <v>0.9253</v>
-      </c>
-      <c r="G8" s="6">
-        <v>0.9777</v>
-      </c>
-      <c r="H8" s="6">
-        <v>0.9507</v>
-      </c>
-      <c r="I8" s="6">
-        <v>0.9064</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="E8" s="5">
+        <v>4.24E-2</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.92530000000000001</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.97770000000000001</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.95069999999999999</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0.90639999999999998</v>
+      </c>
+      <c r="J8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>34</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>0.1484</v>
       </c>
-      <c r="F9" s="6">
-        <v>0.9532</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0.9559</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0.9544</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0.9132</v>
-      </c>
-      <c r="J9" s="4" t="s">
+      <c r="F9" s="5">
+        <v>0.95320000000000005</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.95589999999999997</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.95440000000000003</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.91320000000000001</v>
+      </c>
+      <c r="J9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>14</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>0.17</v>
       </c>
-      <c r="F10" s="6">
-        <v>0.9465</v>
-      </c>
-      <c r="G10" s="6">
-        <v>0.9511</v>
-      </c>
-      <c r="H10" s="6">
-        <v>0.9485</v>
-      </c>
-      <c r="I10" s="6">
-        <v>0.9025</v>
-      </c>
-      <c r="J10" s="4" t="s">
+      <c r="F10" s="5">
+        <v>0.94650000000000001</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.95109999999999995</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.94850000000000001</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0.90249999999999997</v>
+      </c>
+      <c r="J10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>16</v>
       </c>
-      <c r="E11" s="6">
-        <v>0.1683</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0.9421</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0.9555</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0.9484</v>
-      </c>
-      <c r="I11" s="6">
-        <v>0.9023</v>
-      </c>
-      <c r="J11" s="4" t="s">
+      <c r="E11" s="5">
+        <v>0.16830000000000001</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.94210000000000005</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.95550000000000002</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.94840000000000002</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0.90229999999999999</v>
+      </c>
+      <c r="J11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>26</v>
       </c>
-      <c r="E12" s="6">
-        <v>0.0435</v>
-      </c>
-      <c r="F12" s="6">
-        <v>0.9725</v>
-      </c>
-      <c r="G12" s="6">
-        <v>0.9295</v>
-      </c>
-      <c r="H12" s="6">
-        <v>0.9502</v>
-      </c>
-      <c r="I12" s="6">
-        <v>0.9057</v>
-      </c>
-      <c r="J12" s="4" t="s">
+      <c r="E12" s="5">
+        <v>4.3499999999999997E-2</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.97250000000000003</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.92949999999999999</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.95020000000000004</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.90569999999999995</v>
+      </c>
+      <c r="J12" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>23</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.0515</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0.9616</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0.942</v>
-      </c>
-      <c r="H13" s="6">
-        <v>0.9514</v>
-      </c>
-      <c r="I13" s="6">
-        <v>0.9078</v>
-      </c>
-      <c r="J13" s="4" t="s">
+      <c r="E13" s="5">
+        <v>5.1499999999999997E-2</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.96160000000000001</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.95140000000000002</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.90780000000000005</v>
+      </c>
+      <c r="J13" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" t="s">
         <v>32</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>28</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.1468</v>
-      </c>
-      <c r="F14" s="6">
-        <v>0.9619</v>
-      </c>
-      <c r="G14" s="6">
-        <v>0.9471</v>
-      </c>
-      <c r="H14" s="6">
-        <v>0.9543</v>
-      </c>
-      <c r="I14" s="6">
-        <v>0.9129</v>
-      </c>
-      <c r="J14" s="4" t="s">
+      <c r="E14" s="5">
+        <v>0.14680000000000001</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0.96189999999999998</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0.94710000000000005</v>
+      </c>
+      <c r="H14" s="5">
+        <v>0.95430000000000004</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0.91290000000000004</v>
+      </c>
+      <c r="J14" t="s">
         <v>43</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>37</v>
       </c>
-      <c r="E15" s="6">
-        <v>0.1587</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0.9501</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0.9549</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0.9524</v>
-      </c>
-      <c r="I15" s="6">
-        <v>0.9094</v>
-      </c>
-      <c r="J15" s="4" t="s">
+      <c r="E15" s="5">
+        <v>0.15870000000000001</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0.95009999999999994</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.95489999999999997</v>
+      </c>
+      <c r="H15" s="5">
+        <v>0.95240000000000002</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0.90939999999999999</v>
+      </c>
+      <c r="J15" t="s">
         <v>48</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>39</v>
       </c>
-      <c r="E16" s="6">
-        <v>0.1519</v>
-      </c>
-      <c r="F16" s="6">
-        <v>0.9654</v>
-      </c>
-      <c r="G16" s="6">
-        <v>0.9381</v>
-      </c>
-      <c r="H16" s="6">
-        <v>0.9513</v>
-      </c>
-      <c r="I16" s="6">
-        <v>0.9077</v>
-      </c>
-      <c r="J16" s="4" t="s">
+      <c r="E16" s="5">
+        <v>0.15190000000000001</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0.96540000000000004</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.93810000000000004</v>
+      </c>
+      <c r="H16" s="5">
+        <v>0.95130000000000003</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0.90769999999999995</v>
+      </c>
+      <c r="J16" t="s">
         <v>51</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>52</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" t="s">
         <v>53</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>50</v>
       </c>
-      <c r="E17" s="6">
-        <v>0.1488</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0.9552</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0.9531</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0.9539</v>
-      </c>
-      <c r="I17" s="6">
+      <c r="E17" s="5">
+        <v>0.14879999999999999</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0.95520000000000005</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0.95309999999999995</v>
+      </c>
+      <c r="H17" s="5">
+        <v>0.95389999999999997</v>
+      </c>
+      <c r="I17" s="5">
         <v>0.9123</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" t="s">
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>50</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="5">
         <v>0.1767</v>
       </c>
-      <c r="F18" s="6">
-        <v>0.9652</v>
-      </c>
-      <c r="G18" s="6">
-        <v>0.9229</v>
-      </c>
-      <c r="H18" s="6">
-        <v>0.9429</v>
-      </c>
-      <c r="I18" s="6">
-        <v>0.893</v>
-      </c>
-      <c r="J18" s="4" t="s">
+      <c r="F18" s="5">
+        <v>0.96519999999999995</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.92290000000000005</v>
+      </c>
+      <c r="H18" s="5">
+        <v>0.94289999999999996</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="J18" t="s">
         <v>57</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>58</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" t="s">
         <v>59</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>34</v>
       </c>
-      <c r="E19" s="6">
-        <v>0.0682</v>
-      </c>
-      <c r="F19" s="6">
+      <c r="E19" s="5">
+        <v>6.8199999999999997E-2</v>
+      </c>
+      <c r="F19" s="5">
         <v>0.9556</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="5">
         <v>0.9133</v>
       </c>
-      <c r="H19" s="6">
-        <v>0.9331</v>
-      </c>
-      <c r="I19" s="6">
-        <v>0.8761</v>
-      </c>
-      <c r="J19" s="4" t="s">
+      <c r="H19" s="5">
+        <v>0.93310000000000004</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0.87609999999999999</v>
+      </c>
+      <c r="J19" t="s">
         <v>60</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>30</v>
       </c>
-      <c r="E20" s="6">
-        <v>0.1627</v>
-      </c>
-      <c r="F20" s="6">
-        <v>0.9464</v>
-      </c>
-      <c r="G20" s="6">
-        <v>0.9554</v>
-      </c>
-      <c r="H20" s="6">
+      <c r="E20" s="5">
+        <v>0.16270000000000001</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0.94640000000000002</v>
+      </c>
+      <c r="G20" s="5">
+        <v>0.95540000000000003</v>
+      </c>
+      <c r="H20" s="5">
         <v>0.9506</v>
       </c>
-      <c r="I20" s="6">
-        <v>0.9062</v>
-      </c>
-      <c r="J20" s="4" t="s">
+      <c r="I20" s="5">
+        <v>0.90620000000000001</v>
+      </c>
+      <c r="J20" t="s">
         <v>63</v>
       </c>
     </row>
